--- a/AI_워크플로우.xlsx
+++ b/AI_워크플로우.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AI_LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B13AF01-A2B6-4E90-BE11-D460AC91221F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A8F35F-3281-4A69-9D8A-9920DF4F7143}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="155">
   <si>
     <t>분야</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -646,11 +646,6 @@
 프리미엄: $119</t>
   </si>
   <si>
-    <t xml:space="preserve">
-크리에이터: 33,000
-프로: 60,967</t>
-  </si>
-  <si>
     <t xml:space="preserve">무료 플랜의 경우 크레딧, 영상 길이, 해상도 제한 O
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -712,10 +707,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>맹맨지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.vidnoz.com/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -823,6 +814,12 @@
 Starter_€24 
 Pro_€60 
 Business_€800 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+크리에이터: \33,000
+프로: \60,967</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1317,7 +1314,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>16</v>
@@ -1704,19 +1701,19 @@
         <v>120</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.4">
@@ -1736,19 +1733,19 @@
         <v>121</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="156" x14ac:dyDescent="0.4">
@@ -1764,87 +1761,87 @@
       <c r="D16" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>122</v>
+      <c r="E16" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="F16" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="H16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="J16" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="93.6" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J17" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="124.8" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="I18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
